--- a/Tailieu/Nganhangfilegoc/sao_ke_9.xlsx
+++ b/Tailieu/Nganhangfilegoc/sao_ke_9.xlsx
@@ -31,67 +31,55 @@
     <x:t>Số dư</x:t>
   </x:si>
   <x:si>
-    <x:t>03/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN NAM VIET-030826-10:27:09 6215ASCB02TBK9RH</x:t>
+    <x:t>05/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THU PHI DICH VU BDSD THANG 06.2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN MUA MAY CHAM CONG CUA CTY CHIEM BON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nap vao tai khoan cty FT26215650130767 GD 6215IBT1kCTBWQNA 030826-14:53:57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY DIEN MAY CHIEM BON THANH TOAN CHUYEN KHOAN DAI TAI LOC-030826-14:55:25 6215ASCB02T1F86M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>thanh toan hd 40 cho chiem bon GD 6216IBT1fJ98DLFK 040826-14:00:05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>My Nam TT phan mem GD 6219MCOBQ21JS6VS 070826-10:17:50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH BACH NIEN THIEN DUC VUNG TAU TT TIEN NANG CAP SUA CHUA MAY TINH CHO CTY CHIEM BON THEO HD SO 46 NGAY 6.8.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(SoThe:422926******3289)NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO tracenbr:825248 as 2026-08-07:114438</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH MY THUAT SX DV THUONG MAI PHUONG LONG-THEO HD SO 45 KY NGAY 5/8/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(SoThe:422926******3289)NGUYEN QUOC HOANG Rut tien tai ACB ATM PGD LE H PHO tracenbr:887835 as 2026-08-07:040130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANH TOAN LUONG THANG 7 - 2026-100826-13:12:28 6222ASCB02TNVE65</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nap vao tai khoan cong ty FT26233576167159 GD 6233IBT1k2QQXLJD 210826-15:59:03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY CHIEM BON THANH TOAN HD 3442-210826-16:01:27 6233ASCB02RYB1JG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/08/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lai nhap von</x:t>
+    <x:t>07/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NGUYEN THI BINH NOP TIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN LUONG THANG 06 2026 DEN NGUYEN THI BINH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN TIENLUONG T6 2026 DENLE THI NGUYET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN TIEN LUONG THANG 6 2026 DEN NGUYEN VAN VIEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CN THAM DO KHAI THAC DK NAM CONSON TT CHO HOA DON SO: 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRA LAI TIEN GUI TAI KHOAN: 4705167352304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CTY TNHH DV TM KT CONG NGHE VIET CHUYEN TIEN TTHET SO TIEN CON LAI THEO HD SO 0104 HD MB NP NP CNV 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/07/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRA LAI TIEN GUI TAI KHOAN: 5107040176768</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -469,9 +457,9 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="123.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="9.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="106.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="4" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="1" customFormat="1">
@@ -499,13 +487,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C2" s="2">
-        <x:v>1500000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="2">
-        <x:v>455235</x:v>
+        <x:v>17749073</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -513,21 +501,21 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="2">
-        <x:v>2500000</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C3" s="2">
+        <x:v>40000</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="2">
-        <x:v>2955235</x:v>
+        <x:v>17709073</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>9</x:v>
@@ -536,197 +524,197 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="2">
-        <x:v>2000000</x:v>
+        <x:v>50000000</x:v>
       </x:c>
       <x:c r="E4" s="2">
-        <x:v>4955235</x:v>
+        <x:v>67709073</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="2">
-        <x:v>3900000</x:v>
+        <x:v>13100000</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="2">
-        <x:v>1055235</x:v>
+        <x:v>54609073</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="2">
-        <x:v>2500000</x:v>
+      <x:c r="C6" s="2">
+        <x:v>20900</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="2">
-        <x:v>3555235</x:v>
+        <x:v>54588173</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="2">
-        <x:v>5200000</x:v>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="2">
+        <x:v>12152500</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="2">
-        <x:v>8755235</x:v>
+        <x:v>42435673</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="2">
-        <x:v>5690000</x:v>
+      <x:c r="C8" s="2">
+        <x:v>12173400</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8" s="2">
-        <x:v>14445235</x:v>
+        <x:v>30262273</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C9" s="2">
-        <x:v>6500000</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D9" s="2">
+        <x:v>125000000</x:v>
       </x:c>
       <x:c r="E9" s="2">
-        <x:v>7945235</x:v>
+        <x:v>155262273</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="2">
-        <x:v>2260000</x:v>
+        <x:v>522346400</x:v>
       </x:c>
       <x:c r="E10" s="2">
-        <x:v>10205235</x:v>
+        <x:v>677608673</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="2">
-        <x:v>2250000</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="2">
+        <x:v>628055</x:v>
       </x:c>
       <x:c r="E11" s="2">
-        <x:v>7955235</x:v>
+        <x:v>678236728</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C12" s="2">
-        <x:v>7500000</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D12" s="2">
+        <x:v>500000000</x:v>
       </x:c>
       <x:c r="E12" s="2">
-        <x:v>455235</x:v>
+        <x:v>1178236728</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D13" s="2">
-        <x:v>1512000</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C13" s="2">
+        <x:v>232236</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E13" s="2">
-        <x:v>1967235</x:v>
+        <x:v>1178004492</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C14" s="2">
-        <x:v>1296000</x:v>
+        <x:v>844496000</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="2">
-        <x:v>671235</x:v>
+        <x:v>333508492</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="2">
-        <x:v>18</x:v>
+        <x:v>57161</x:v>
       </x:c>
       <x:c r="E15" s="2">
-        <x:v>671253</x:v>
+        <x:v>333565653</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Tailieu/Nganhangfilegoc/sao_ke_9.xlsx
+++ b/Tailieu/Nganhangfilegoc/sao_ke_9.xlsx
@@ -16,79 +16,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Ngày giao dịch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Diễn giải</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ghi nợ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ghi có</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Số dư</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THU PHI DICH VU BDSD THANG 06.2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>07/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NGUYEN THI BINH NOP TIEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN LUONG THANG 06 2026 DEN NGUYEN THI BINH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN TIENLUONG T6 2026 DENLE THI NGUYET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH DV TM KT CONG NGHE VIET THANH TOAN TIEN LUONG THANG 6 2026 DEN NGUYEN VAN VIEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CN THAM DO KHAI THAC DK NAM CONSON TT CHO HOA DON SO: 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRA LAI TIEN GUI TAI KHOAN: 4705167352304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CTY TNHH DV TM KT CONG NGHE VIET CHUYEN TIEN TTHET SO TIEN CON LAI THEO HD SO 0104 HD MB NP NP CNV 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28/07/2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRA LAI TIEN GUI TAI KHOAN: 5107040176768</x:t>
+    <x:t>test</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="164" formatCode="#,##0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -134,27 +70,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -453,268 +382,15 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E15"/>
+  <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="106.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="4" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="4.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" s="1" customFormat="1">
+    <x:row r="1" spans="1:1" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="2">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E2" s="2">
-        <x:v>17749073</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="2">
-        <x:v>40000</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="2">
-        <x:v>17709073</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2">
-        <x:v>50000000</x:v>
-      </x:c>
-      <x:c r="E4" s="2">
-        <x:v>67709073</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="2">
-        <x:v>13100000</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E5" s="2">
-        <x:v>54609073</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="A6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C6" s="2">
-        <x:v>20900</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E6" s="2">
-        <x:v>54588173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5">
-      <x:c r="A7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C7" s="2">
-        <x:v>12152500</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E7" s="2">
-        <x:v>42435673</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="2">
-        <x:v>12173400</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E8" s="2">
-        <x:v>30262273</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="2">
-        <x:v>125000000</x:v>
-      </x:c>
-      <x:c r="E9" s="2">
-        <x:v>155262273</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="2">
-        <x:v>522346400</x:v>
-      </x:c>
-      <x:c r="E10" s="2">
-        <x:v>677608673</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:5">
-      <x:c r="A11" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="2">
-        <x:v>628055</x:v>
-      </x:c>
-      <x:c r="E11" s="2">
-        <x:v>678236728</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:5">
-      <x:c r="A12" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="2">
-        <x:v>500000000</x:v>
-      </x:c>
-      <x:c r="E12" s="2">
-        <x:v>1178236728</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:5">
-      <x:c r="A13" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C13" s="2">
-        <x:v>232236</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E13" s="2">
-        <x:v>1178004492</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5">
-      <x:c r="A14" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C14" s="2">
-        <x:v>844496000</x:v>
-      </x:c>
-      <x:c r="D14" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E14" s="2">
-        <x:v>333508492</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:5">
-      <x:c r="A15" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="2">
-        <x:v>57161</x:v>
-      </x:c>
-      <x:c r="E15" s="2">
-        <x:v>333565653</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
